--- a/artfynd/A 63693-2019 artfynd.xlsx
+++ b/artfynd/A 63693-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63693-2019 artfynd.xlsx
+++ b/artfynd/A 63693-2019 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>96276963</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 63693-2019 artfynd.xlsx
+++ b/artfynd/A 63693-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,120 +1045,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>96276963</v>
-      </c>
-      <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Överkalix, Nb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>839664</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7419941</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Erik Edler</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Erik Edler</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
